--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18744,7 +18744,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21108,7 +21108,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30564,7 +30564,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31746,7 +31746,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -34110,7 +34110,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35292,7 +35292,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36474,7 +36474,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42384,7 +42384,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43566,7 +43566,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48300,7 +48300,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -49878,7 +49878,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -51456,7 +51456,7 @@
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -53034,7 +53034,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -54612,7 +54612,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -56190,7 +56190,7 @@
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -57768,7 +57768,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -59346,7 +59346,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -60924,7 +60924,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -62502,7 +62502,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -64080,7 +64080,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -65658,7 +65658,7 @@
       </c>
       <c r="AM331" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN331" t="b">
@@ -67236,7 +67236,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -68814,7 +68814,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -70392,7 +70392,7 @@
       </c>
       <c r="AM355" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN355" t="b">
@@ -71970,7 +71970,7 @@
       </c>
       <c r="AM363" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN363" t="b">
@@ -73548,7 +73548,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -75126,7 +75126,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -76704,7 +76704,7 @@
       </c>
       <c r="AM387" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN387" t="b">
@@ -78282,7 +78282,7 @@
       </c>
       <c r="AM395" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN395" t="b">
@@ -79860,7 +79860,7 @@
       </c>
       <c r="AM403" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN403" t="b">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25826,7 +25826,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27008,7 +27008,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32918,7 +32918,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38828,7 +38828,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40010,7 +40010,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41192,7 +41192,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45134,7 +45134,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46316,7 +46316,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46712,7 +46712,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -47894,7 +47894,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48290,7 +48290,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -49472,7 +49472,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49868,7 +49868,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -51050,7 +51050,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51446,7 +51446,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -52628,7 +52628,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -54206,7 +54206,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -54602,7 +54602,7 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
@@ -55784,7 +55784,7 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
@@ -56180,7 +56180,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -57362,7 +57362,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -57758,7 +57758,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -58940,7 +58940,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59336,7 +59336,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -60518,7 +60518,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60914,7 +60914,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -62096,7 +62096,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62492,7 +62492,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -63674,7 +63674,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -64070,7 +64070,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
@@ -65252,7 +65252,7 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
@@ -65648,7 +65648,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="AJ337" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK337" t="inlineStr">
@@ -67226,7 +67226,7 @@
       </c>
       <c r="AJ339" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK339" t="inlineStr">
@@ -68408,7 +68408,7 @@
       </c>
       <c r="AJ345" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK345" t="inlineStr">
@@ -68804,7 +68804,7 @@
       </c>
       <c r="AJ347" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK347" t="inlineStr">
@@ -69986,7 +69986,7 @@
       </c>
       <c r="AJ353" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK353" t="inlineStr">
@@ -70382,7 +70382,7 @@
       </c>
       <c r="AJ355" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK355" t="inlineStr">
@@ -71564,7 +71564,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -71960,7 +71960,7 @@
       </c>
       <c r="AJ363" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK363" t="inlineStr">
@@ -73142,7 +73142,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73538,7 +73538,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -74720,7 +74720,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -75116,7 +75116,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -76298,7 +76298,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -76694,7 +76694,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -77876,7 +77876,7 @@
       </c>
       <c r="AJ393" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK393" t="inlineStr">
@@ -78272,7 +78272,7 @@
       </c>
       <c r="AJ395" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK395" t="inlineStr">
@@ -79454,7 +79454,7 @@
       </c>
       <c r="AJ401" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK401" t="inlineStr">
@@ -79850,7 +79850,7 @@
       </c>
       <c r="AJ403" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK403" t="inlineStr">
@@ -81032,7 +81032,7 @@
       </c>
       <c r="AJ409" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK409" t="inlineStr">

--- a/diseases/d068/2000-2004.xlsx
+++ b/diseases/d068/2000-2004.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20712,7 +20712,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21894,7 +21894,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23076,7 +23076,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26622,7 +26622,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28986,7 +28986,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -30168,7 +30168,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31350,7 +31350,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32532,7 +32532,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33714,7 +33714,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -36078,7 +36078,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37260,7 +37260,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38442,7 +38442,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40806,7 +40806,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41988,7 +41988,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -43170,7 +43170,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44352,7 +44352,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45930,7 +45930,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47508,7 +47508,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -49086,7 +49086,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -50664,7 +50664,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -52242,7 +52242,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -53820,7 +53820,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -55398,7 +55398,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -56976,7 +56976,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -58554,7 +58554,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -60132,7 +60132,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -61710,7 +61710,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -63288,7 +63288,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -64866,7 +64866,7 @@
       </c>
       <c r="AM327" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN327" t="b">
@@ -66444,7 +66444,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -68022,7 +68022,7 @@
       </c>
       <c r="AM343" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN343" t="b">
@@ -69600,7 +69600,7 @@
       </c>
       <c r="AM351" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN351" t="b">
@@ -71178,7 +71178,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -72756,7 +72756,7 @@
       </c>
       <c r="AM367" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN367" t="b">
@@ -74334,7 +74334,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -75912,7 +75912,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -77490,7 +77490,7 @@
       </c>
       <c r="AM391" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN391" t="b">
@@ -79068,7 +79068,7 @@
       </c>
       <c r="AM399" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN399" t="b">
@@ -80646,7 +80646,7 @@
       </c>
       <c r="AM407" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN407" t="b">
